--- a/Assets/StreamingAssets/Configurations/Coop.xlsx
+++ b/Assets/StreamingAssets/Configurations/Coop.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity\VTuberSim\Assets\StreamingAssets\Configurations\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{A1687C12-2C51-426F-B3AD-1E2950BBE29D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{26089D1B-0756-4F35-831A-E192745A1168}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="360" windowWidth="38640" windowHeight="21120" xr2:uid="{85C794E5-BD16-4817-A60E-1226C928BE3E}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{85C794E5-BD16-4817-A60E-1226C928BE3E}"/>
   </bookViews>
   <sheets>
     <sheet name="CoopEvents" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
   <si>
     <t>ID</t>
   </si>
@@ -42,9 +42,6 @@
     <t>EventTypes</t>
   </si>
   <si>
-    <t>Effects</t>
-  </si>
-  <si>
     <t>UnlockLevel</t>
   </si>
   <si>
@@ -55,6 +52,30 @@
   </si>
   <si>
     <t>Description</t>
+  </si>
+  <si>
+    <t>Recovery</t>
+  </si>
+  <si>
+    <t>Effect1</t>
+  </si>
+  <si>
+    <t>E1Param</t>
+  </si>
+  <si>
+    <t>Effect2</t>
+  </si>
+  <si>
+    <t>E2Param</t>
+  </si>
+  <si>
+    <t>Effect3</t>
+  </si>
+  <si>
+    <t>E3Param</t>
+  </si>
+  <si>
+    <t>Stream,Practice</t>
   </si>
 </sst>
 </file>
@@ -78,9 +99,18 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFFF0000"/>
+      </left>
       <right/>
       <top/>
       <bottom/>
@@ -90,8 +120,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -406,36 +437,91 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{094FDAA9-F479-41E4-9B48-92DE073E19D4}">
-  <dimension ref="A1:G1"/>
+  <dimension ref="A1:L3"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="4" width="12" customWidth="1"/>
     <col min="5" max="5" width="12.7109375" customWidth="1"/>
     <col min="6" max="6" width="25.42578125" customWidth="1"/>
-    <col min="7" max="7" width="18.7109375" customWidth="1"/>
+    <col min="7" max="7" width="9.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1" t="s">
         <v>5</v>
       </c>
-      <c r="C1" t="s">
-        <v>6</v>
-      </c>
       <c r="D1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E1" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F1" t="s">
         <v>1</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1" t="s">
+        <v>8</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1" t="s">
+        <v>10</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="L1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A2">
+        <v>0</v>
+      </c>
+      <c r="B2">
+        <v>1</v>
+      </c>
+      <c r="C2">
         <v>2</v>
+      </c>
+      <c r="D2">
+        <v>0.5</v>
+      </c>
+      <c r="E2">
+        <v>0</v>
+      </c>
+      <c r="F2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A3">
+        <v>1</v>
+      </c>
+      <c r="B3">
+        <v>1</v>
+      </c>
+      <c r="C3">
+        <v>2</v>
+      </c>
+      <c r="D3">
+        <v>0.7</v>
+      </c>
+      <c r="E3">
+        <v>0</v>
+      </c>
+      <c r="F3" t="s">
+        <v>13</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/StreamingAssets/Configurations/Coop.xlsx
+++ b/Assets/StreamingAssets/Configurations/Coop.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity\VTuberSim\Assets\StreamingAssets\Configurations\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{26089D1B-0756-4F35-831A-E192745A1168}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8BC8FFEE-EE0D-47B3-8C2E-33E80CDD0A99}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{85C794E5-BD16-4817-A60E-1226C928BE3E}"/>
   </bookViews>
@@ -503,6 +503,12 @@
       <c r="F2" t="s">
         <v>6</v>
       </c>
+      <c r="G2">
+        <v>15</v>
+      </c>
+      <c r="H2">
+        <v>100000</v>
+      </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A3">

--- a/Assets/StreamingAssets/Configurations/Coop.xlsx
+++ b/Assets/StreamingAssets/Configurations/Coop.xlsx
@@ -1,25 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
-  <workbookPr defaultThemeVersion="166925"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity\VTuberSim\Assets\StreamingAssets\Configurations\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8BC8FFEE-EE0D-47B3-8C2E-33E80CDD0A99}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+  <workbookPr/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{85C794E5-BD16-4817-A60E-1226C928BE3E}"/>
+    <workbookView windowWidth="24750" windowHeight="10480"/>
   </bookViews>
   <sheets>
     <sheet name="CoopEvents" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
         <xcalcf:feature name="microsoft.com:RD"/>
@@ -27,6 +18,8 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -34,29 +27,26 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="39">
   <si>
     <t>ID</t>
   </si>
   <si>
+    <t>Name</t>
+  </si>
+  <si>
+    <t>Description</t>
+  </si>
+  <si>
+    <t>Probability</t>
+  </si>
+  <si>
+    <t>UnlockLevel</t>
+  </si>
+  <si>
     <t>EventTypes</t>
   </si>
   <si>
-    <t>UnlockLevel</t>
-  </si>
-  <si>
-    <t>Probability</t>
-  </si>
-  <si>
-    <t>Name</t>
-  </si>
-  <si>
-    <t>Description</t>
-  </si>
-  <si>
-    <t>Recovery</t>
-  </si>
-  <si>
     <t>Effect1</t>
   </si>
   <si>
@@ -75,31 +65,452 @@
     <t>E3Param</t>
   </si>
   <si>
-    <t>Stream,Practice</t>
+    <t>小室帮助1</t>
+  </si>
+  <si>
+    <t>练习后体力+2</t>
+  </si>
+  <si>
+    <t>Practice</t>
+  </si>
+  <si>
+    <t>小室帮助2</t>
+  </si>
+  <si>
+    <t>协助/外出后粉丝+50</t>
+  </si>
+  <si>
+    <t>Stream,Work</t>
+  </si>
+  <si>
+    <t>雪王帮助1</t>
+  </si>
+  <si>
+    <t>休息后沪币+5</t>
+  </si>
+  <si>
+    <t>Rest</t>
+  </si>
+  <si>
+    <t>雪王帮助2</t>
+  </si>
+  <si>
+    <t>协助/外出后杂谈力+8</t>
+  </si>
+  <si>
+    <t>Outside,Coop</t>
+  </si>
+  <si>
+    <t>井井帮助1</t>
+  </si>
+  <si>
+    <t>协助后体力+2</t>
+  </si>
+  <si>
+    <t>Coop</t>
+  </si>
+  <si>
+    <t>井井帮助2</t>
+  </si>
+  <si>
+    <t>练习/休息后歌力+8</t>
+  </si>
+  <si>
+    <t>Practice,Rest</t>
+  </si>
+  <si>
+    <t>mama帮助1</t>
+  </si>
+  <si>
+    <t>工作后粉丝+20</t>
+  </si>
+  <si>
+    <t>Work</t>
+  </si>
+  <si>
+    <t>mama帮助2</t>
+  </si>
+  <si>
+    <t>休息后体力+7</t>
+  </si>
+  <si>
+    <t>柚子茶帮助1</t>
+  </si>
+  <si>
+    <t>练习后沪币+5</t>
+  </si>
+  <si>
+    <t>柚子茶帮助2</t>
+  </si>
+  <si>
+    <t>工作/直播后游戏力+8</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="21">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="33">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -116,25 +527,315 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+  <cellStyles count="49">
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -183,7 +884,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
+        <a:latin typeface="Calibri Light"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック Light"/>
@@ -216,26 +917,9 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック"/>
@@ -268,23 +952,6 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -426,112 +1093,324 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
-  <a:extLst>
-    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
-    </a:ext>
-  </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{094FDAA9-F479-41E4-9B48-92DE073E19D4}">
-  <dimension ref="A1:L3"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:L11"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="4" width="12" customWidth="1"/>
-    <col min="5" max="5" width="12.7109375" customWidth="1"/>
-    <col min="6" max="6" width="25.42578125" customWidth="1"/>
-    <col min="7" max="7" width="9.140625" customWidth="1"/>
+    <col min="1" max="2" width="12" customWidth="1"/>
+    <col min="3" max="3" width="20.0833333333333" customWidth="1"/>
+    <col min="4" max="4" width="12" customWidth="1"/>
+    <col min="5" max="5" width="12.7083333333333" customWidth="1"/>
+    <col min="6" max="6" width="25.425" customWidth="1"/>
+    <col min="7" max="7" width="9.14166666666667" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:12">
       <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D1" t="s">
         <v>3</v>
       </c>
       <c r="E1" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F1" t="s">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" t="s">
         <v>7</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="J1" t="s">
         <v>9</v>
       </c>
-      <c r="J1" t="s">
+      <c r="K1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="L1" t="s">
         <v>11</v>
       </c>
-      <c r="L1" t="s">
-        <v>12</v>
-      </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8">
       <c r="A2">
         <v>0</v>
       </c>
-      <c r="B2">
-        <v>1</v>
-      </c>
-      <c r="C2">
-        <v>2</v>
+      <c r="B2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C2" t="s">
+        <v>13</v>
       </c>
       <c r="D2">
-        <v>0.5</v>
+        <v>0.2</v>
       </c>
       <c r="E2">
         <v>0</v>
       </c>
       <c r="F2" t="s">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="G2">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="H2">
-        <v>100000</v>
+        <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8">
       <c r="A3">
         <v>1</v>
       </c>
-      <c r="B3">
-        <v>1</v>
-      </c>
-      <c r="C3">
+      <c r="B3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C3" t="s">
+        <v>16</v>
+      </c>
+      <c r="D3">
+        <v>0.3</v>
+      </c>
+      <c r="E3">
         <v>2</v>
       </c>
-      <c r="D3">
-        <v>0.7</v>
-      </c>
-      <c r="E3">
+      <c r="F3" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G3">
+        <v>15</v>
+      </c>
+      <c r="H3">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8">
+      <c r="A4">
+        <v>2</v>
+      </c>
+      <c r="B4" t="s">
+        <v>18</v>
+      </c>
+      <c r="C4" t="s">
+        <v>19</v>
+      </c>
+      <c r="D4">
+        <v>0.5</v>
+      </c>
+      <c r="E4">
         <v>0</v>
       </c>
-      <c r="F3" t="s">
-        <v>13</v>
+      <c r="F4" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="G4">
+        <v>5</v>
+      </c>
+      <c r="H4">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8">
+      <c r="A5">
+        <v>3</v>
+      </c>
+      <c r="B5" t="s">
+        <v>21</v>
+      </c>
+      <c r="C5" t="s">
+        <v>22</v>
+      </c>
+      <c r="D5">
+        <v>0.2</v>
+      </c>
+      <c r="E5">
+        <v>2</v>
+      </c>
+      <c r="F5" t="s">
+        <v>23</v>
+      </c>
+      <c r="G5">
+        <v>30</v>
+      </c>
+      <c r="H5">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8">
+      <c r="A6">
+        <v>4</v>
+      </c>
+      <c r="B6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C6" t="s">
+        <v>25</v>
+      </c>
+      <c r="D6">
+        <v>0.3</v>
+      </c>
+      <c r="E6">
+        <v>0</v>
+      </c>
+      <c r="F6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G6">
+        <v>3</v>
+      </c>
+      <c r="H6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8">
+      <c r="A7">
+        <v>5</v>
+      </c>
+      <c r="B7" t="s">
+        <v>27</v>
+      </c>
+      <c r="C7" t="s">
+        <v>28</v>
+      </c>
+      <c r="D7">
+        <v>0.2</v>
+      </c>
+      <c r="E7">
+        <v>2</v>
+      </c>
+      <c r="F7" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="G7">
+        <v>28</v>
+      </c>
+      <c r="H7">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8">
+      <c r="A8">
+        <v>6</v>
+      </c>
+      <c r="B8" t="s">
+        <v>30</v>
+      </c>
+      <c r="C8" t="s">
+        <v>31</v>
+      </c>
+      <c r="D8">
+        <v>0.3</v>
+      </c>
+      <c r="E8">
+        <v>0</v>
+      </c>
+      <c r="F8" t="s">
+        <v>32</v>
+      </c>
+      <c r="G8">
+        <v>15</v>
+      </c>
+      <c r="H8">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8">
+      <c r="A9">
+        <v>7</v>
+      </c>
+      <c r="B9" t="s">
+        <v>33</v>
+      </c>
+      <c r="C9" t="s">
+        <v>34</v>
+      </c>
+      <c r="D9">
+        <v>0.2</v>
+      </c>
+      <c r="E9">
+        <v>2</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="G9">
+        <v>3</v>
+      </c>
+      <c r="H9">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8">
+      <c r="A10">
+        <v>8</v>
+      </c>
+      <c r="B10" t="s">
+        <v>35</v>
+      </c>
+      <c r="C10" t="s">
+        <v>36</v>
+      </c>
+      <c r="D10">
+        <v>0.2</v>
+      </c>
+      <c r="E10">
+        <v>0</v>
+      </c>
+      <c r="F10" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="G10">
+        <v>5</v>
+      </c>
+      <c r="H10">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8">
+      <c r="A11">
+        <v>9</v>
+      </c>
+      <c r="B11" t="s">
+        <v>37</v>
+      </c>
+      <c r="C11" t="s">
+        <v>38</v>
+      </c>
+      <c r="D11">
+        <v>0.2</v>
+      </c>
+      <c r="E11">
+        <v>2</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G11">
+        <v>29</v>
+      </c>
+      <c r="H11">
+        <v>8</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId1"/>
+  <pageSetup paperSize="1" orientation="portrait"/>
+  <headerFooter/>
 </worksheet>
 </file>
--- a/Assets/StreamingAssets/Configurations/Coop.xlsx
+++ b/Assets/StreamingAssets/Configurations/Coop.xlsx
@@ -156,14 +156,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="21">
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
+  <fonts count="20">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -628,148 +621,148 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -777,7 +770,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
   </cellXfs>
@@ -1148,7 +1141,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:8">
+    <row r="2" spans="1:10">
       <c r="A2">
         <v>0</v>
       </c>
@@ -1173,8 +1166,14 @@
       <c r="H2">
         <v>2</v>
       </c>
+      <c r="I2">
+        <v>31</v>
+      </c>
+      <c r="J2">
+        <v>5</v>
+      </c>
     </row>
-    <row r="3" spans="1:8">
+    <row r="3" spans="1:10">
       <c r="A3">
         <v>1</v>
       </c>
@@ -1199,8 +1198,14 @@
       <c r="H3">
         <v>50</v>
       </c>
+      <c r="I3">
+        <v>31</v>
+      </c>
+      <c r="J3">
+        <v>5</v>
+      </c>
     </row>
-    <row r="4" spans="1:8">
+    <row r="4" spans="1:10">
       <c r="A4">
         <v>2</v>
       </c>
@@ -1225,8 +1230,14 @@
       <c r="H4">
         <v>5</v>
       </c>
+      <c r="I4">
+        <v>32</v>
+      </c>
+      <c r="J4">
+        <v>5</v>
+      </c>
     </row>
-    <row r="5" spans="1:8">
+    <row r="5" spans="1:10">
       <c r="A5">
         <v>3</v>
       </c>
@@ -1251,8 +1262,14 @@
       <c r="H5">
         <v>8</v>
       </c>
+      <c r="I5">
+        <v>32</v>
+      </c>
+      <c r="J5">
+        <v>5</v>
+      </c>
     </row>
-    <row r="6" spans="1:8">
+    <row r="6" spans="1:10">
       <c r="A6">
         <v>4</v>
       </c>
@@ -1277,8 +1294,14 @@
       <c r="H6">
         <v>2</v>
       </c>
+      <c r="I6">
+        <v>33</v>
+      </c>
+      <c r="J6">
+        <v>5</v>
+      </c>
     </row>
-    <row r="7" spans="1:8">
+    <row r="7" spans="1:10">
       <c r="A7">
         <v>5</v>
       </c>
@@ -1303,8 +1326,14 @@
       <c r="H7">
         <v>8</v>
       </c>
+      <c r="I7">
+        <v>33</v>
+      </c>
+      <c r="J7">
+        <v>5</v>
+      </c>
     </row>
-    <row r="8" spans="1:8">
+    <row r="8" spans="1:10">
       <c r="A8">
         <v>6</v>
       </c>
@@ -1329,8 +1358,14 @@
       <c r="H8">
         <v>20</v>
       </c>
+      <c r="I8">
+        <v>35</v>
+      </c>
+      <c r="J8">
+        <v>5</v>
+      </c>
     </row>
-    <row r="9" spans="1:8">
+    <row r="9" spans="1:10">
       <c r="A9">
         <v>7</v>
       </c>
@@ -1355,8 +1390,14 @@
       <c r="H9">
         <v>7</v>
       </c>
+      <c r="I9">
+        <v>35</v>
+      </c>
+      <c r="J9">
+        <v>5</v>
+      </c>
     </row>
-    <row r="10" spans="1:8">
+    <row r="10" spans="1:10">
       <c r="A10">
         <v>8</v>
       </c>
@@ -1381,8 +1422,14 @@
       <c r="H10">
         <v>5</v>
       </c>
+      <c r="I10">
+        <v>34</v>
+      </c>
+      <c r="J10">
+        <v>5</v>
+      </c>
     </row>
-    <row r="11" spans="1:8">
+    <row r="11" spans="1:10">
       <c r="A11">
         <v>9</v>
       </c>
@@ -1406,6 +1453,12 @@
       </c>
       <c r="H11">
         <v>8</v>
+      </c>
+      <c r="I11">
+        <v>34</v>
+      </c>
+      <c r="J11">
+        <v>5</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/StreamingAssets/Configurations/Coop.xlsx
+++ b/Assets/StreamingAssets/Configurations/Coop.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29029"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity\VTuberSim\Assets\StreamingAssets\Configurations\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DCC5302D-C3FD-42D1-A2DD-4260B4C3439D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView windowWidth="24750" windowHeight="10480"/>
+    <workbookView xWindow="25490" yWindow="-110" windowWidth="25820" windowHeight="13900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="CoopEvents" sheetId="1" r:id="rId1"/>
@@ -18,8 +24,6 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -149,368 +153,32 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="4">
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-  </numFmts>
-  <fonts count="21">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="等线"/>
+      <name val="Calibri"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="等线"/>
+      <name val="Calibri"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
-  <fills count="33">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="10">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -527,315 +195,28 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="49">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
   </cellXfs>
-  <cellStyles count="49">
-    <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
-    <cellStyle name="货币" xfId="2" builtinId="4"/>
-    <cellStyle name="百分比" xfId="3" builtinId="5"/>
-    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
-    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
-    <cellStyle name="超链接" xfId="6" builtinId="8"/>
-    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
-    <cellStyle name="注释" xfId="8" builtinId="10"/>
-    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
-    <cellStyle name="标题" xfId="10" builtinId="15"/>
-    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
-    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
-    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
-    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
-    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
-    <cellStyle name="输入" xfId="16" builtinId="20"/>
-    <cellStyle name="输出" xfId="17" builtinId="21"/>
-    <cellStyle name="计算" xfId="18" builtinId="22"/>
-    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
-    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
-    <cellStyle name="汇总" xfId="21" builtinId="25"/>
-    <cellStyle name="好" xfId="22" builtinId="26"/>
-    <cellStyle name="差" xfId="23" builtinId="27"/>
-    <cellStyle name="适中" xfId="24" builtinId="28"/>
-    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
-    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
-    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
-    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
-    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
-    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
-    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
+  <cellStyles count="1">
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -1093,21 +474,21 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:L11"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="2" width="12" customWidth="1"/>
-    <col min="3" max="3" width="20.0833333333333" customWidth="1"/>
+    <col min="3" max="3" width="20.140625" customWidth="1"/>
     <col min="4" max="4" width="12" customWidth="1"/>
-    <col min="5" max="5" width="12.7083333333333" customWidth="1"/>
-    <col min="6" max="6" width="25.425" customWidth="1"/>
-    <col min="7" max="7" width="9.14166666666667" customWidth="1"/>
+    <col min="5" max="5" width="12.7109375" customWidth="1"/>
+    <col min="6" max="6" width="25.42578125" customWidth="1"/>
+    <col min="7" max="7" width="9.140625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:12">
@@ -1148,7 +529,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:8">
+    <row r="2" spans="1:12">
       <c r="A2">
         <v>0</v>
       </c>
@@ -1174,7 +555,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:8">
+    <row r="3" spans="1:12">
       <c r="A3">
         <v>1</v>
       </c>
@@ -1190,7 +571,7 @@
       <c r="E3">
         <v>2</v>
       </c>
-      <c r="F3" s="2" t="s">
+      <c r="F3" t="s">
         <v>17</v>
       </c>
       <c r="G3">
@@ -1200,7 +581,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="4" spans="1:8">
+    <row r="4" spans="1:12">
       <c r="A4">
         <v>2</v>
       </c>
@@ -1216,7 +597,7 @@
       <c r="E4">
         <v>0</v>
       </c>
-      <c r="F4" s="2" t="s">
+      <c r="F4" t="s">
         <v>20</v>
       </c>
       <c r="G4">
@@ -1226,7 +607,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="5" spans="1:8">
+    <row r="5" spans="1:12">
       <c r="A5">
         <v>3</v>
       </c>
@@ -1252,7 +633,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="6" spans="1:8">
+    <row r="6" spans="1:12">
       <c r="A6">
         <v>4</v>
       </c>
@@ -1278,7 +659,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="7" spans="1:8">
+    <row r="7" spans="1:12">
       <c r="A7">
         <v>5</v>
       </c>
@@ -1294,7 +675,7 @@
       <c r="E7">
         <v>2</v>
       </c>
-      <c r="F7" s="3" t="s">
+      <c r="F7" s="2" t="s">
         <v>29</v>
       </c>
       <c r="G7">
@@ -1304,7 +685,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="8" spans="1:8">
+    <row r="8" spans="1:12">
       <c r="A8">
         <v>6</v>
       </c>
@@ -1330,7 +711,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="9" spans="1:8">
+    <row r="9" spans="1:12">
       <c r="A9">
         <v>7</v>
       </c>
@@ -1346,7 +727,7 @@
       <c r="E9">
         <v>2</v>
       </c>
-      <c r="F9" s="2" t="s">
+      <c r="F9" t="s">
         <v>20</v>
       </c>
       <c r="G9">
@@ -1356,7 +737,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="10" spans="1:8">
+    <row r="10" spans="1:12">
       <c r="A10">
         <v>8</v>
       </c>
@@ -1372,7 +753,7 @@
       <c r="E10">
         <v>0</v>
       </c>
-      <c r="F10" s="3" t="s">
+      <c r="F10" s="2" t="s">
         <v>14</v>
       </c>
       <c r="G10">
@@ -1382,7 +763,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="11" spans="1:8">
+    <row r="11" spans="1:12">
       <c r="A11">
         <v>9</v>
       </c>
@@ -1398,7 +779,7 @@
       <c r="E11">
         <v>2</v>
       </c>
-      <c r="F11" s="2" t="s">
+      <c r="F11" t="s">
         <v>17</v>
       </c>
       <c r="G11">
@@ -1410,7 +791,6 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="1" orientation="portrait"/>
-  <headerFooter/>
+  <pageSetup orientation="portrait"/>
 </worksheet>
 </file>
--- a/Assets/StreamingAssets/Configurations/Coop.xlsx
+++ b/Assets/StreamingAssets/Configurations/Coop.xlsx
@@ -1,16 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29029"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity\VTuberSim\Assets\StreamingAssets\Configurations\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B21463A3-F44F-446F-A3DF-F7034DC5B031}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView windowWidth="22190" windowHeight="9040"/>
   </bookViews>
   <sheets>
     <sheet name="CoopEvents" sheetId="1" r:id="rId1"/>
@@ -24,6 +18,8 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -75,18 +71,27 @@
     <t>练习后体力+2</t>
   </si>
   <si>
+    <t>Practice</t>
+  </si>
+  <si>
     <t>小室帮助2</t>
   </si>
   <si>
     <t>协助/外出后粉丝+50</t>
   </si>
   <si>
+    <t>Stream1,Work</t>
+  </si>
+  <si>
     <t>雪王帮助1</t>
   </si>
   <si>
     <t>休息后沪币+5</t>
   </si>
   <si>
+    <t>Rest</t>
+  </si>
+  <si>
     <t>雪王帮助2</t>
   </si>
   <si>
@@ -102,6 +107,9 @@
     <t>协助后体力+2</t>
   </si>
   <si>
+    <t>Coop</t>
+  </si>
+  <si>
     <t>井井帮助2</t>
   </si>
   <si>
@@ -117,6 +125,9 @@
     <t>工作后粉丝+20</t>
   </si>
   <si>
+    <t>Work</t>
+  </si>
+  <si>
     <t>mama帮助2</t>
   </si>
   <si>
@@ -135,46 +146,367 @@
     <t>工作/直播后游戏力+8</t>
   </si>
   <si>
-    <t>Stream1,Work</t>
-  </si>
-  <si>
     <t>Stream0,Work</t>
-  </si>
-  <si>
-    <t>Practice</t>
-  </si>
-  <si>
-    <t>Rest</t>
-  </si>
-  <si>
-    <t>Coop</t>
-  </si>
-  <si>
-    <t>Work</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="20">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="等线"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="33">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -191,9 +523,251 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
   <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
@@ -202,17 +776,61 @@
       <alignment vertical="top"/>
     </xf>
   </cellXfs>
-  <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+  <cellStyles count="49">
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -470,21 +1088,21 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:L11"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col min="1" max="2" width="12" customWidth="1"/>
-    <col min="3" max="3" width="20.140625" customWidth="1"/>
+    <col min="3" max="3" width="20.1416666666667" customWidth="1"/>
     <col min="4" max="4" width="12" customWidth="1"/>
-    <col min="5" max="5" width="12.7109375" customWidth="1"/>
-    <col min="6" max="6" width="25.42578125" customWidth="1"/>
-    <col min="7" max="7" width="9.140625" customWidth="1"/>
+    <col min="5" max="5" width="12.7083333333333" customWidth="1"/>
+    <col min="6" max="6" width="25.425" customWidth="1"/>
+    <col min="7" max="7" width="9.14166666666667" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:12">
@@ -525,7 +1143,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:12">
+    <row r="2" spans="1:10">
       <c r="A2">
         <v>0</v>
       </c>
@@ -542,7 +1160,7 @@
         <v>0</v>
       </c>
       <c r="F2" t="s">
-        <v>36</v>
+        <v>14</v>
       </c>
       <c r="G2">
         <v>3</v>
@@ -557,15 +1175,15 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:12">
+    <row r="3" spans="1:10">
       <c r="A3">
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D3">
         <v>0.3</v>
@@ -574,7 +1192,7 @@
         <v>2</v>
       </c>
       <c r="F3" t="s">
-        <v>34</v>
+        <v>17</v>
       </c>
       <c r="G3">
         <v>15</v>
@@ -589,15 +1207,15 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:12">
+    <row r="4" spans="1:10">
       <c r="A4">
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C4" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="D4">
         <v>0.5</v>
@@ -606,7 +1224,7 @@
         <v>0</v>
       </c>
       <c r="F4" t="s">
-        <v>37</v>
+        <v>20</v>
       </c>
       <c r="G4">
         <v>5</v>
@@ -621,15 +1239,15 @@
         <v>5</v>
       </c>
     </row>
-    <row r="5" spans="1:12">
+    <row r="5" spans="1:10">
       <c r="A5">
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="C5" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="D5">
         <v>0.2</v>
@@ -638,7 +1256,7 @@
         <v>2</v>
       </c>
       <c r="F5" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="G5">
         <v>30</v>
@@ -653,15 +1271,15 @@
         <v>5</v>
       </c>
     </row>
-    <row r="6" spans="1:12">
+    <row r="6" spans="1:10">
       <c r="A6">
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="C6" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="D6">
         <v>0.3</v>
@@ -670,7 +1288,7 @@
         <v>0</v>
       </c>
       <c r="F6" t="s">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="G6">
         <v>3</v>
@@ -685,15 +1303,15 @@
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:12">
+    <row r="7" spans="1:10">
       <c r="A7">
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="C7" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="D7">
         <v>0.2</v>
@@ -702,7 +1320,7 @@
         <v>2</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="G7">
         <v>28</v>
@@ -717,15 +1335,15 @@
         <v>5</v>
       </c>
     </row>
-    <row r="8" spans="1:12">
+    <row r="8" spans="1:10">
       <c r="A8">
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="C8" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="D8">
         <v>0.3</v>
@@ -734,7 +1352,7 @@
         <v>0</v>
       </c>
       <c r="F8" t="s">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="G8">
         <v>15</v>
@@ -749,15 +1367,15 @@
         <v>5</v>
       </c>
     </row>
-    <row r="9" spans="1:12">
+    <row r="9" spans="1:10">
       <c r="A9">
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="C9" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="D9">
         <v>0.2</v>
@@ -766,7 +1384,7 @@
         <v>2</v>
       </c>
       <c r="F9" t="s">
-        <v>37</v>
+        <v>20</v>
       </c>
       <c r="G9">
         <v>3</v>
@@ -781,15 +1399,15 @@
         <v>5</v>
       </c>
     </row>
-    <row r="10" spans="1:12">
+    <row r="10" spans="1:10">
       <c r="A10">
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="C10" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="D10">
         <v>0.2</v>
@@ -798,7 +1416,7 @@
         <v>0</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>36</v>
+        <v>14</v>
       </c>
       <c r="G10">
         <v>5</v>
@@ -813,15 +1431,15 @@
         <v>5</v>
       </c>
     </row>
-    <row r="11" spans="1:12">
+    <row r="11" spans="1:10">
       <c r="A11">
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="C11" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="D11">
         <v>0.2</v>
@@ -830,7 +1448,7 @@
         <v>2</v>
       </c>
       <c r="F11" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="G11">
         <v>29</v>
@@ -847,6 +1465,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait"/>
+  <pageSetup paperSize="1" orientation="portrait"/>
+  <headerFooter/>
 </worksheet>
 </file>
--- a/Assets/StreamingAssets/Configurations/Coop.xlsx
+++ b/Assets/StreamingAssets/Configurations/Coop.xlsx
@@ -68,85 +68,85 @@
     <t>小室帮助1</t>
   </si>
   <si>
-    <t>练习后体力+2</t>
+    <t>直播后体力+2</t>
+  </si>
+  <si>
+    <t>Stream</t>
+  </si>
+  <si>
+    <t>小室帮助2</t>
+  </si>
+  <si>
+    <t>协助/外出后粉丝+50</t>
+  </si>
+  <si>
+    <t>Stream,Work</t>
+  </si>
+  <si>
+    <t>雪王帮助1</t>
+  </si>
+  <si>
+    <t>休息后沪币+5</t>
+  </si>
+  <si>
+    <t>Rest</t>
+  </si>
+  <si>
+    <t>雪王帮助2</t>
+  </si>
+  <si>
+    <t>协助/外出后杂谈力+8</t>
+  </si>
+  <si>
+    <t>Outside,Coop</t>
+  </si>
+  <si>
+    <t>井井帮助1</t>
+  </si>
+  <si>
+    <t>协助后体力+2</t>
+  </si>
+  <si>
+    <t>Coop</t>
+  </si>
+  <si>
+    <t>井井帮助2</t>
+  </si>
+  <si>
+    <t>练习/休息后歌力+8</t>
+  </si>
+  <si>
+    <t>Practice,Rest</t>
+  </si>
+  <si>
+    <t>mama帮助1</t>
+  </si>
+  <si>
+    <t>工作后粉丝+20</t>
+  </si>
+  <si>
+    <t>Work</t>
+  </si>
+  <si>
+    <t>mama帮助2</t>
+  </si>
+  <si>
+    <t>休息后体力+7</t>
+  </si>
+  <si>
+    <t>柚子茶帮助1</t>
+  </si>
+  <si>
+    <t>练习后沪币+5</t>
   </si>
   <si>
     <t>Practice</t>
   </si>
   <si>
-    <t>小室帮助2</t>
-  </si>
-  <si>
-    <t>协助/外出后粉丝+50</t>
-  </si>
-  <si>
-    <t>Stream1,Work</t>
-  </si>
-  <si>
-    <t>雪王帮助1</t>
-  </si>
-  <si>
-    <t>休息后沪币+5</t>
-  </si>
-  <si>
-    <t>Rest</t>
-  </si>
-  <si>
-    <t>雪王帮助2</t>
-  </si>
-  <si>
-    <t>协助/外出后杂谈力+8</t>
-  </si>
-  <si>
-    <t>Outside,Coop</t>
-  </si>
-  <si>
-    <t>井井帮助1</t>
-  </si>
-  <si>
-    <t>协助后体力+2</t>
-  </si>
-  <si>
-    <t>Coop</t>
-  </si>
-  <si>
-    <t>井井帮助2</t>
-  </si>
-  <si>
-    <t>练习/休息后歌力+8</t>
-  </si>
-  <si>
-    <t>Practice,Rest</t>
-  </si>
-  <si>
-    <t>mama帮助1</t>
-  </si>
-  <si>
-    <t>工作后粉丝+20</t>
-  </si>
-  <si>
-    <t>Work</t>
-  </si>
-  <si>
-    <t>mama帮助2</t>
-  </si>
-  <si>
-    <t>休息后体力+7</t>
-  </si>
-  <si>
-    <t>柚子茶帮助1</t>
-  </si>
-  <si>
-    <t>练习后沪币+5</t>
-  </si>
-  <si>
     <t>柚子茶帮助2</t>
   </si>
   <si>
     <t>工作/直播后游戏力+8</t>
-  </si>
-  <si>
-    <t>Stream0,Work</t>
   </si>
 </sst>
 </file>
@@ -1416,7 +1416,7 @@
         <v>0</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>14</v>
+        <v>37</v>
       </c>
       <c r="G10">
         <v>5</v>
@@ -1436,10 +1436,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C11" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D11">
         <v>0.2</v>
@@ -1448,7 +1448,7 @@
         <v>2</v>
       </c>
       <c r="F11" t="s">
-        <v>39</v>
+        <v>17</v>
       </c>
       <c r="G11">
         <v>29</v>

--- a/Assets/StreamingAssets/Configurations/Coop.xlsx
+++ b/Assets/StreamingAssets/Configurations/Coop.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="22190" windowHeight="9040"/>
+    <workbookView windowWidth="24750" windowHeight="10480"/>
   </bookViews>
   <sheets>
     <sheet name="CoopEvents" sheetId="1" r:id="rId1"/>
@@ -86,7 +86,7 @@
     <t>雪王帮助1</t>
   </si>
   <si>
-    <t>休息后沪币+5</t>
+    <t>休息后杂谈力+5</t>
   </si>
   <si>
     <t>Rest</t>
@@ -104,10 +104,10 @@
     <t>井井帮助1</t>
   </si>
   <si>
-    <t>协助后体力+2</t>
-  </si>
-  <si>
-    <t>Coop</t>
+    <t>外出后歌力+5</t>
+  </si>
+  <si>
+    <t>Outside</t>
   </si>
   <si>
     <t>井井帮助2</t>
@@ -122,7 +122,7 @@
     <t>mama帮助1</t>
   </si>
   <si>
-    <t>工作后粉丝+20</t>
+    <t>工作后粉丝+50</t>
   </si>
   <si>
     <t>Work</t>
@@ -137,7 +137,7 @@
     <t>柚子茶帮助1</t>
   </si>
   <si>
-    <t>练习后沪币+5</t>
+    <t>练习后游戏力+5</t>
   </si>
   <si>
     <t>Practice</t>
@@ -1227,7 +1227,7 @@
         <v>20</v>
       </c>
       <c r="G4">
-        <v>5</v>
+        <v>30</v>
       </c>
       <c r="H4">
         <v>5</v>
@@ -1291,10 +1291,10 @@
         <v>26</v>
       </c>
       <c r="G6">
-        <v>3</v>
+        <v>28</v>
       </c>
       <c r="H6">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="I6">
         <v>33</v>
@@ -1358,7 +1358,7 @@
         <v>15</v>
       </c>
       <c r="H8">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="I8">
         <v>35</v>
@@ -1419,7 +1419,7 @@
         <v>37</v>
       </c>
       <c r="G10">
-        <v>5</v>
+        <v>29</v>
       </c>
       <c r="H10">
         <v>5</v>

--- a/Assets/StreamingAssets/Configurations/Coop.xlsx
+++ b/Assets/StreamingAssets/Configurations/Coop.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="24750" windowHeight="10480"/>
+    <workbookView windowWidth="22190" windowHeight="9040"/>
   </bookViews>
   <sheets>
     <sheet name="CoopEvents" sheetId="1" r:id="rId1"/>

--- a/Assets/StreamingAssets/Configurations/Coop.xlsx
+++ b/Assets/StreamingAssets/Configurations/Coop.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="22190" windowHeight="9040"/>
+    <workbookView windowWidth="24550" windowHeight="10380"/>
   </bookViews>
   <sheets>
     <sheet name="CoopEvents" sheetId="1" r:id="rId1"/>
@@ -71,7 +71,7 @@
     <t>直播后体力+2</t>
   </si>
   <si>
-    <t>Stream</t>
+    <t>Coop</t>
   </si>
   <si>
     <t>小室帮助2</t>

--- a/Assets/StreamingAssets/Configurations/Coop.xlsx
+++ b/Assets/StreamingAssets/Configurations/Coop.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="24550" windowHeight="10380"/>
+    <workbookView windowWidth="30720" windowHeight="13380"/>
   </bookViews>
   <sheets>
     <sheet name="CoopEvents" sheetId="1" r:id="rId1"/>
@@ -119,7 +119,7 @@
     <t>Practice,Rest</t>
   </si>
   <si>
-    <t>mama帮助1</t>
+    <t>糯糯帮助1</t>
   </si>
   <si>
     <t>工作后粉丝+50</t>
@@ -128,13 +128,13 @@
     <t>Work</t>
   </si>
   <si>
-    <t>mama帮助2</t>
+    <t>糯糯帮助2</t>
   </si>
   <si>
     <t>休息后体力+7</t>
   </si>
   <si>
-    <t>柚子茶帮助1</t>
+    <t>柚茶帮助1</t>
   </si>
   <si>
     <t>练习后游戏力+5</t>
@@ -143,7 +143,7 @@
     <t>Practice</t>
   </si>
   <si>
-    <t>柚子茶帮助2</t>
+    <t>柚茶帮助2</t>
   </si>
   <si>
     <t>工作/直播后游戏力+8</t>
@@ -1095,14 +1095,14 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:L11"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8"/>
   <cols>
     <col min="1" max="2" width="12" customWidth="1"/>
-    <col min="3" max="3" width="20.1416666666667" customWidth="1"/>
+    <col min="3" max="3" width="20.1388888888889" customWidth="1"/>
     <col min="4" max="4" width="12" customWidth="1"/>
-    <col min="5" max="5" width="12.7083333333333" customWidth="1"/>
-    <col min="6" max="6" width="25.425" customWidth="1"/>
-    <col min="7" max="7" width="9.14166666666667" customWidth="1"/>
+    <col min="5" max="5" width="12.7037037037037" customWidth="1"/>
+    <col min="6" max="6" width="25.4259259259259" customWidth="1"/>
+    <col min="7" max="7" width="9.13888888888889" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:12">

--- a/Assets/StreamingAssets/Configurations/Coop.xlsx
+++ b/Assets/StreamingAssets/Configurations/Coop.xlsx
@@ -1,16 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29328"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity\VTuberSim\Assets\StreamingAssets\Configurations\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{29D3604A-EBC7-4456-9D66-8866F6B8FCA0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3420" yWindow="3420" windowWidth="28800" windowHeight="15225" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView windowWidth="24750" windowHeight="10030"/>
   </bookViews>
   <sheets>
     <sheet name="CoopEvents" sheetId="1" r:id="rId1"/>
@@ -24,6 +18,8 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -72,116 +68,452 @@
     <t>小室帮助1</t>
   </si>
   <si>
+    <t>社交后体力+2|小室好感度+5</t>
+  </si>
+  <si>
     <t>Coop</t>
   </si>
   <si>
     <t>小室帮助2</t>
   </si>
   <si>
+    <t>直播/工作后粉丝+50|小室好感度+5</t>
+  </si>
+  <si>
     <t>Stream,Work</t>
   </si>
   <si>
     <t>雪王帮助1</t>
   </si>
   <si>
+    <t>休息后杂谈力+5|雪王好感度+5</t>
+  </si>
+  <si>
     <t>Rest</t>
   </si>
   <si>
     <t>雪王帮助2</t>
   </si>
   <si>
+    <t>社交/外出后杂谈力+8|雪王好感度+5</t>
+  </si>
+  <si>
     <t>Outside,Coop</t>
   </si>
   <si>
     <t>井井帮助1</t>
   </si>
   <si>
+    <t>外出后歌力+5|井井好感度+5</t>
+  </si>
+  <si>
     <t>Outside</t>
   </si>
   <si>
     <t>井井帮助2</t>
   </si>
   <si>
+    <t>练习/休息后歌力+8|井井好感度+5</t>
+  </si>
+  <si>
     <t>Practice,Rest</t>
   </si>
   <si>
     <t>糯糯帮助1</t>
   </si>
   <si>
+    <t>工作后粉丝+50|糯糯好感度+5</t>
+  </si>
+  <si>
     <t>Work</t>
   </si>
   <si>
     <t>糯糯帮助2</t>
   </si>
   <si>
+    <t>休息后体力+7|糯糯好感度+5</t>
+  </si>
+  <si>
     <t>柚茶帮助1</t>
   </si>
   <si>
+    <t>练习后游戏力+5|柚茶好感度+5</t>
+  </si>
+  <si>
     <t>Practice</t>
   </si>
   <si>
     <t>柚茶帮助2</t>
   </si>
   <si>
-    <t>直播后体力+2|小室好感度+5</t>
-  </si>
-  <si>
-    <t>协助/外出后粉丝+50|小室好感度+5</t>
-  </si>
-  <si>
     <t>工作/直播后游戏力+8|柚茶好感度+5</t>
-  </si>
-  <si>
-    <t>练习后游戏力+5|柚茶好感度+5</t>
-  </si>
-  <si>
-    <t>休息后体力+7|糯糯好感度+5</t>
-  </si>
-  <si>
-    <t>工作后粉丝+50|糯糯好感度+5</t>
-  </si>
-  <si>
-    <t>练习/休息后歌力+8|井井好感度+5</t>
-  </si>
-  <si>
-    <t>外出后歌力+5|井井好感度+5</t>
-  </si>
-  <si>
-    <t>协助/外出后杂谈力+8|雪王好感度+5</t>
-  </si>
-  <si>
-    <t>休息后杂谈力+5|雪王好感度+5</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="21">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="等线"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="33">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -198,29 +530,315 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
   <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
-  <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+  <cellStyles count="49">
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -478,21 +1096,21 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:L11"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col min="1" max="2" width="12" customWidth="1"/>
     <col min="3" max="3" width="39" customWidth="1"/>
     <col min="4" max="4" width="12" customWidth="1"/>
-    <col min="5" max="5" width="12.7109375" customWidth="1"/>
-    <col min="6" max="6" width="25.42578125" customWidth="1"/>
-    <col min="7" max="7" width="9.140625" customWidth="1"/>
+    <col min="5" max="5" width="12.7083333333333" customWidth="1"/>
+    <col min="6" max="6" width="25.425" customWidth="1"/>
+    <col min="7" max="7" width="9.14166666666667" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:12">
@@ -540,8 +1158,8 @@
       <c r="B2" t="s">
         <v>12</v>
       </c>
-      <c r="C2" s="3" t="s">
-        <v>30</v>
+      <c r="C2" s="2" t="s">
+        <v>13</v>
       </c>
       <c r="D2">
         <v>0.2</v>
@@ -550,7 +1168,7 @@
         <v>0</v>
       </c>
       <c r="F2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G2">
         <v>3</v>
@@ -570,10 +1188,10 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>14</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>31</v>
+        <v>15</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>16</v>
       </c>
       <c r="D3">
         <v>0.3</v>
@@ -582,7 +1200,7 @@
         <v>2</v>
       </c>
       <c r="F3" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="G3">
         <v>15</v>
@@ -602,10 +1220,10 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C4" t="s">
-        <v>39</v>
+        <v>19</v>
       </c>
       <c r="D4">
         <v>0.5</v>
@@ -614,7 +1232,7 @@
         <v>0</v>
       </c>
       <c r="F4" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="G4">
         <v>30</v>
@@ -634,10 +1252,10 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="C5" t="s">
-        <v>38</v>
+        <v>22</v>
       </c>
       <c r="D5">
         <v>0.2</v>
@@ -646,7 +1264,7 @@
         <v>2</v>
       </c>
       <c r="F5" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="G5">
         <v>30</v>
@@ -666,10 +1284,10 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>20</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>37</v>
+        <v>24</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="D6">
         <v>0.3</v>
@@ -678,7 +1296,7 @@
         <v>0</v>
       </c>
       <c r="F6" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="G6">
         <v>28</v>
@@ -698,10 +1316,10 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="C7" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="D7">
         <v>0.2</v>
@@ -709,8 +1327,8 @@
       <c r="E7">
         <v>2</v>
       </c>
-      <c r="F7" s="2" t="s">
-        <v>23</v>
+      <c r="F7" s="3" t="s">
+        <v>29</v>
       </c>
       <c r="G7">
         <v>28</v>
@@ -730,10 +1348,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="C8" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="D8">
         <v>0.3</v>
@@ -742,7 +1360,7 @@
         <v>0</v>
       </c>
       <c r="F8" t="s">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="G8">
         <v>15</v>
@@ -762,7 +1380,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="C9" t="s">
         <v>34</v>
@@ -774,7 +1392,7 @@
         <v>2</v>
       </c>
       <c r="F9" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="G9">
         <v>3</v>
@@ -794,10 +1412,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="C10" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="D10">
         <v>0.2</v>
@@ -805,8 +1423,8 @@
       <c r="E10">
         <v>0</v>
       </c>
-      <c r="F10" s="2" t="s">
-        <v>28</v>
+      <c r="F10" s="3" t="s">
+        <v>37</v>
       </c>
       <c r="G10">
         <v>29</v>
@@ -826,10 +1444,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="C11" t="s">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="D11">
         <v>0.2</v>
@@ -838,7 +1456,7 @@
         <v>2</v>
       </c>
       <c r="F11" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="G11">
         <v>29</v>
@@ -855,6 +1473,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait"/>
+  <pageSetup paperSize="1" orientation="portrait"/>
+  <headerFooter/>
 </worksheet>
 </file>